--- a/tame_output/ON/bt/strategyON_20240329.xlsx
+++ b/tame_output/ON/bt/strategyON_20240329.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.6%</t>
+          <t>-68.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>110.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-539.9%</t>
+          <t>-569.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>-46.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-61.9%</t>
+          <t>-62.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.8%</t>
+          <t>510.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-403.7%</t>
+          <t>-407.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-228.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.3%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-61.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.9%</t>
+          <t>-166.3%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>-0.099250136941057</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.081272283236556</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>-0.0952586841458668</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.080693660473872</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2009865069470839</v>
+        <v>-0.4934071150991274</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.036329422858449</v>
+        <v>2.919361179597631</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4226084405052014</v>
+        <v>-0.7150290486572449</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.947546866034124</v>
+        <v>2.830578622773306</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6306124988582786</v>
+        <v>-0.9230331070103222</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.869237387246818</v>
+        <v>2.752269143986</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.901012461567164</v>
+        <v>-1.193433069719207</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.756158858501252</v>
+        <v>2.639190615240434</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.240170839155686</v>
+        <v>-1.53259144730773</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.613579806772292</v>
+        <v>2.496611563511475</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.860608669035209</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.385742964559251</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.857271922526237</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.395176413571408</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-2.223982974192783</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.249598384948522</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.316742756970812</v>
+        <v>-2.609163365122855</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.211037010650174</v>
+        <v>2.094068767389357</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.660425530197474</v>
+        <v>-2.952846138349518</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.075333024814125</v>
+        <v>1.958364781553307</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.018075880435823</v>
+        <v>-3.310496488587866</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.928378943375043</v>
+        <v>1.811410700114226</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.02473682065797</v>
+        <v>-3.317157428810014</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.927487493986444</v>
+        <v>1.810519250725626</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.456542613807758</v>
+        <v>-3.748963221959802</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.741098064193933</v>
+        <v>1.624129820933116</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.782975142675502</v>
+        <v>-4.075395750827546</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.598809827648927</v>
+        <v>1.481841584388109</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.784539293785805</v>
+        <v>-4.076959901937849</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.596764758860771</v>
+        <v>1.479796515599953</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.148165538686118</v>
+        <v>-4.440586146838163</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.457801821134887</v>
+        <v>1.340833577874069</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.145738474157399</v>
+        <v>-4.438159082309444</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.458027161952206</v>
+        <v>1.341058918691388</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.554327251338078</v>
+        <v>-4.846747859490122</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.293353195094693</v>
+        <v>1.176384951833875</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.967309735479172</v>
+        <v>-5.259730343631216</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.123345633909716</v>
+        <v>1.006377390648899</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.383701609766169</v>
+        <v>-5.676122217918214</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9547829348037946</v>
+        <v>0.8378146915429769</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.760378620296014</v>
+        <v>-6.052799228448058</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8143708212605358</v>
+        <v>0.6974025779997182</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.774093484621125</v>
+        <v>-6.066514092773169</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8049844406761864</v>
+        <v>0.6880161974153687</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.086918283866105</v>
+        <v>-6.379338892018149</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6782594410331955</v>
+        <v>0.5612911977723778</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.091731322331442</v>
+        <v>-6.384151930483486</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.680113201576269</v>
+        <v>0.5631449583154513</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.525080430441678</v>
+        <v>-6.817501038593722</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5027472537977715</v>
+        <v>0.3857790105369538</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.908081819184309</v>
+        <v>-7.200502427336353</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3494445969791347</v>
+        <v>0.232476353718317</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.283067145355586</v>
+        <v>-7.57548775350763</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2020219824820542</v>
+        <v>0.08505373922123649</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.642597467859588</v>
+        <v>-7.935018076011632</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0635601567785038</v>
+        <v>-0.05340808648231388</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.968997496524601</v>
+        <v>-8.261418104676645</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05908383473032419</v>
+        <v>-0.1760520779911419</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.962521349731041</v>
+        <v>-8.254941957883085</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.05345162539113124</v>
+        <v>-0.1704198686519489</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.95883042477463</v>
+        <v>-8.251251032926675</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05197525540856685</v>
+        <v>-0.168943498669385</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.163088600104492</v>
+        <v>-8.455509208256538</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1281653284218693</v>
+        <v>-0.2451335716826879</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.904356262408918</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.323727626592857</v>
+        <v>-8.616148234744903</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1879383845327793</v>
+        <v>-0.3049066277935979</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.019089735411313</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.250257794925409</v>
+        <v>-8.542678403077455</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1431787503723787</v>
+        <v>-0.2601469936331973</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.945619903743865</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.425382212311952</v>
+        <v>-8.717802820463998</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1986732965794795</v>
+        <v>-0.3156415398402976</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.120744321130409</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.659834306326442</v>
+        <v>-8.952254914478488</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2996732990868711</v>
+        <v>-0.4166415423476897</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.120744321130409</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.94763815086368</v>
+        <v>-9.240058759015726</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4214670276757428</v>
+        <v>-0.5384352709365614</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.408548165667647</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.177462598027505</v>
+        <v>-9.469883206179551</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5122810167027163</v>
+        <v>-0.6292492599635349</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.571195702737807</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.409491517763767</v>
+        <v>-9.701912125915813</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6023988559681066</v>
+        <v>-0.7193670992289252</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.633208399926231</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.357476003794954</v>
+        <v>-9.649896611947</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5776023146941807</v>
+        <v>-0.6945705579549988</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.633208399926231</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.438767933349158</v>
+        <v>-9.731188541501204</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6115943134146038</v>
+        <v>-0.7285625566754224</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.633208399926231</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.241498527621161</v>
+        <v>-9.533919135773207</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5176331409585329</v>
+        <v>-0.634601384219351</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.435938994198232</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.042346420384062</v>
+        <v>-9.334767028536108</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4510234317103761</v>
+        <v>-0.5679916749711946</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.270616468248419</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.816501267664652</v>
+        <v>-9.108921875816698</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3511062975864037</v>
+        <v>-0.4680745408472218</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.228689792661255</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.530226455341957</v>
+        <v>-8.822647063494003</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2354572281012666</v>
+        <v>-0.3524254713620851</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.228689792661255</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.303430628268623</v>
+        <v>-8.595851236420669</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.1421051231098254</v>
+        <v>-0.2590733663706439</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.160575848039711</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.019521897339875</v>
+        <v>-8.31194250549192</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.02280792649968966</v>
+        <v>-0.1397761697605078</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.160575848039711</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.772534647146922</v>
+        <v>-8.064955255298969</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.06624971118362621</v>
+        <v>-0.05071853207719235</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.913588597846759</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.508697779942853</v>
+        <v>-7.8011183880949</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.1619009767523463</v>
+        <v>0.04493273349152771</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.913588597846759</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.241455979074456</v>
+        <v>-7.533876587226503</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.2669631366003311</v>
+        <v>0.1499948933395125</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.913588597846759</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.965646815673972</v>
+        <v>-7.258067423826019</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.3769864869870641</v>
+        <v>0.2600182437262455</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.824569289568025</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.696579227906993</v>
+        <v>-6.98899983605904</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.4852820282393497</v>
+        <v>0.3683137849785307</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.555501701801046</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.432519289584197</v>
+        <v>-6.724939897736244</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.577645687406716</v>
+        <v>0.460677444145897</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.29144176347825</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.725439666079359</v>
+        <v>-6.017860274231405</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.8576905031483504</v>
+        <v>0.7407222598875314</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.29144176347825</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.475798636093407</v>
+        <v>-5.768219244245453</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.9578905390305725</v>
+        <v>0.8409222957697535</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.041800733492298</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.221256736752331</v>
+        <v>-5.513677344904378</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.05907411998776</v>
+        <v>0.9421058767269406</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.7872588341512228</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.987775514522732</v>
+        <v>-5.28019612267478</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.160391037717452</v>
+        <v>1.043422794456633</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.5537776119216242</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.808066984378859</v>
+        <v>-5.100487592530907</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.229382239462042</v>
+        <v>1.112413996201222</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.4966061077589281</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.675791510747973</v>
+        <v>-4.968212118900021</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.277659915661423</v>
+        <v>1.160691672400604</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.3643306341280415</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.48519183607482</v>
+        <v>-4.777612444226868</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.356714846218321</v>
+        <v>1.239746602957502</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.1737309594548886</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.236192037391239</v>
+        <v>-4.528612645543287</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.469221106915412</v>
+        <v>1.352252863654593</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.1737309594548886</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.044812962530299</v>
+        <v>-4.337233570682347</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.417796807260569</v>
+        <v>1.30082856399975</v>
       </c>
       <c r="F1908" t="n">
         <v>0.01764811540605149</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.765785666874672</v>
+        <v>-4.05820627502672</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.577952067399907</v>
+        <v>1.460983824139087</v>
       </c>
       <c r="F1909" t="n">
         <v>0.01764811540605149</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.48904749220386</v>
+        <v>-3.781468100355907</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.692026349254226</v>
+        <v>1.575058105993407</v>
       </c>
       <c r="F1910" t="n">
         <v>0.1994647765159773</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.36215508576879</v>
+        <v>-3.654575693920838</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.734069325574776</v>
+        <v>1.617101082313957</v>
       </c>
       <c r="F1911" t="n">
         <v>0.3263571829510472</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.174567577858863</v>
+        <v>-3.466988186010911</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.802143716643653</v>
+        <v>1.685175473382834</v>
       </c>
       <c r="F1912" t="n">
         <v>0.3263571829510472</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.932419184405005</v>
+        <v>-3.224839792557053</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.91346542840634</v>
+        <v>1.796497185145521</v>
       </c>
       <c r="F1913" t="n">
         <v>0.3263571829510472</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.869189812636657</v>
+        <v>-3.161610420788704</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.933289297572874</v>
+        <v>1.816321054312055</v>
       </c>
       <c r="F1914" t="n">
         <v>0.3263571829510472</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.68270212025965</v>
+        <v>-2.975122728411698</v>
       </c>
       <c r="E1915" t="n">
-        <v>2.005382468534254</v>
+        <v>1.888414225273435</v>
       </c>
       <c r="F1915" t="n">
         <v>0.5128448753280535</v>
@@ -45619,10 +45619,10 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-2.661552921356207</v>
+        <v>-2.953973529508255</v>
       </c>
       <c r="E1916" t="n">
-        <v>2.021543126332957</v>
+        <v>1.904574883072138</v>
       </c>
       <c r="F1916" t="n">
         <v>0.5339940742314968</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.425974421473325</v>
+        <v>3.55900588344475</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.421185350868811</v>
+        <v>-2.456550622957137</v>
       </c>
       <c r="E1917" t="n">
-        <v>2.113470862874966</v>
+        <v>2.099324754039635</v>
       </c>
       <c r="F1917" t="n">
         <v>0.5339940742314968</v>

--- a/tame_output/ON/bt/strategyON_20240329.xlsx
+++ b/tame_output/ON/bt/strategyON_20240329.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-69.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.5%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.4%</t>
+          <t>-64.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>510.2%</t>
+          <t>509.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-407.2%</t>
+          <t>-432.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-61.5%</t>
+          <t>-60.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.3%</t>
+          <t>-176.4%</t>
         </is>
       </c>
     </row>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781948</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567243</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.55900588344475</v>
+        <v>3.559005883444752</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.456550622957137</v>
+        <v>-2.71020808752481</v>
       </c>
       <c r="E1917" t="n">
-        <v>2.099324754039635</v>
+        <v>1.997861768212566</v>
       </c>
       <c r="F1917" t="n">
         <v>0.5339940742314968</v>

--- a/tame_output/ON/bt/strategyON_20240329.xlsx
+++ b/tame_output/ON/bt/strategyON_20240329.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.3%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-20.1%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>125.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>-65.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-105.8%</t>
+          <t>-155.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1917"/>
+  <dimension ref="A1:G1918"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.559005883444752</v>
+        <v>3.829079198497429</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45652,6 +45652,29 @@
       </c>
       <c r="G1917" t="n">
         <v>3.402697872075136</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="2" t="n">
+        <v>45380</v>
+      </c>
+      <c r="B1918" t="n">
+        <v>3.563423497364743</v>
+      </c>
+      <c r="C1918" t="n">
+        <v>2.91570302597819</v>
+      </c>
+      <c r="D1918" t="n">
+        <v>-2.71020808752481</v>
+      </c>
+      <c r="E1918" t="n">
+        <v>1.997861768212566</v>
+      </c>
+      <c r="F1918" t="n">
+        <v>0.5339940742314968</v>
+      </c>
+      <c r="G1918" t="n">
+        <v>2.908766822964557</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240329.xlsx
+++ b/tame_output/ON/bt/strategyON_20240329.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-28.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.8%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>125.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-569.1%</t>
+          <t>-575.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.2%</t>
+          <t>-67.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>509.4%</t>
+          <t>509.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-432.6%</t>
+          <t>-467.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-228.0%</t>
+          <t>-230.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-37.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-60.9%</t>
+          <t>-67.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.4%</t>
+          <t>-190.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-316.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.1%</t>
+          <t>-161.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-170.6%</t>
+          <t>-206.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-190.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-163.6%</t>
         </is>
       </c>
     </row>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.099250136941057</v>
+        <v>0.1931704712109866</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.081272283236556</v>
+        <v>3.198240526497373</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.0952586841458668</v>
+        <v>-0.1572386040778024</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.080693660473872</v>
+        <v>3.055901692501098</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.494192487848576</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.015669051155112</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4934071150991274</v>
+        <v>-0.555387035031063</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.919361179597631</v>
+        <v>2.894569211624857</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.450444584979295</v>
+        <v>1.096044056895316</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.987347200938607</v>
+        <v>3.774706884088219</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7150290486572449</v>
+        <v>-0.7770089685891806</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.830578622773306</v>
+        <v>2.805786654800531</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.412918451291926</v>
+        <v>1.058517923207946</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.964697737325107</v>
+        <v>3.752057420474719</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9230331070103222</v>
+        <v>-0.9850130269422578</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.752269143986</v>
+        <v>2.727477176013226</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.412918451291926</v>
+        <v>1.058517923207946</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.969589881879032</v>
+        <v>3.756949565028644</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.193433069719207</v>
+        <v>-1.255412989651143</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.639190615240434</v>
+        <v>2.61439864726766</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.14251848858304</v>
+        <v>0.7881179604990611</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.802431360591689</v>
+        <v>3.589791043741302</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.53259144730773</v>
+        <v>-1.594571367239665</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.496611563511475</v>
+        <v>2.4718195955387</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8033601109945183</v>
+        <v>0.4489595829105391</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.592020633345025</v>
+        <v>3.379380316494637</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.860608669035209</v>
+        <v>-1.922588588967144</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.385742964559251</v>
+        <v>2.360950996586477</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4753428892670392</v>
+        <v>0.1209423611830599</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.415548590047305</v>
+        <v>3.202908273196918</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.857271922526237</v>
+        <v>-1.919251842458173</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.395176413571408</v>
+        <v>2.370384445598634</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4780349216860705</v>
+        <v>0.1236343936020913</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.425262559907293</v>
+        <v>3.212622243056905</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.223982974192783</v>
+        <v>-2.285962894124719</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.249598384948522</v>
+        <v>2.224806416975748</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1113238700195249</v>
+        <v>-0.2430766580644543</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.206342320951098</v>
+        <v>2.99370200410071</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.609163365122855</v>
+        <v>-2.671143285054791</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.094068767389357</v>
+        <v>2.069276799416582</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1113238700195249</v>
+        <v>-0.2430766580644543</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.204884859763961</v>
+        <v>2.992244542913574</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.952846138349518</v>
+        <v>-3.014826058281454</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.958364781553307</v>
+        <v>1.933572813580533</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.003417817992306726</v>
+        <v>-0.3509827100916725</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.141910352002246</v>
+        <v>2.929270035151859</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.310496488587866</v>
+        <v>-3.372476408519802</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.811410700114226</v>
+        <v>1.786618732141452</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.7086330603300206</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.923426200515495</v>
+        <v>2.710785883665108</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.317157428810014</v>
+        <v>-3.37913734874195</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.810519250725626</v>
+        <v>1.785727282752852</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.7086330603300206</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.925199127215755</v>
+        <v>2.712558810365367</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.748963221959802</v>
+        <v>-3.810943141891737</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.624129820933116</v>
+        <v>1.599337852960342</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4906500286873084</v>
+        <v>-0.8450505567712876</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.829681516818399</v>
+        <v>2.617041199968011</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.075395750827546</v>
+        <v>-4.137375670759481</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.481841584388109</v>
+        <v>1.457049616415335</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.9275188072784357</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.768485341516201</v>
+        <v>2.555845024665814</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.076959901937849</v>
+        <v>-4.138939821869784</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.479796515599953</v>
+        <v>1.455004547627179</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.9275188072784357</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.767065933172166</v>
+        <v>2.554425616321779</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.440586146838163</v>
+        <v>-4.502566066770098</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.340833577874069</v>
+        <v>1.316041609901295</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6713399160615824</v>
+        <v>-1.025740444145562</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.714620511286132</v>
+        <v>2.501980194435744</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.438159082309444</v>
+        <v>-4.500139002241379</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.341058918691388</v>
+        <v>1.316266950718614</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.671672697868734</v>
+        <v>-1.026073225952713</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.713675357207673</v>
+        <v>2.501035040357285</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.846747859490122</v>
+        <v>-4.908727779422058</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.176384951833875</v>
+        <v>1.151592983861101</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.434662003133392</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.467283634914025</v>
+        <v>2.254643318063637</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.259730343631216</v>
+        <v>-5.321710263563152</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.006377390648899</v>
+        <v>0.9815854226761243</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.434662003133392</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.462469067385485</v>
+        <v>2.249828750535098</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.676122217918214</v>
+        <v>-5.73810213785015</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8378146915429769</v>
+        <v>0.8130227235702026</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.434662003133392</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.460463117994363</v>
+        <v>2.247822801143975</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.052799228448058</v>
+        <v>-6.114779148379994</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.6974025779997182</v>
+        <v>0.6726106100269438</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.434662003133392</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.470721808663042</v>
+        <v>2.258081491812654</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.066514092773169</v>
+        <v>-6.128494012705105</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6880161974153687</v>
+        <v>0.6632242294425943</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.434662003133392</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.466821373808737</v>
+        <v>2.254181056958349</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.379338892018149</v>
+        <v>-6.441318811950085</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5612911977723778</v>
+        <v>0.5364992297996034</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.434662003133392</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.465226293863738</v>
+        <v>2.25258597701335</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.384151930483486</v>
+        <v>-6.446131850415422</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5631449583154513</v>
+        <v>0.5383529903426769</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.436208637836177</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.468077288971275</v>
+        <v>2.255436972120887</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.817501038593722</v>
+        <v>-6.879480958525658</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3857790105369538</v>
+        <v>0.3609870425641795</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.436208637836177</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.464050984436871</v>
+        <v>2.251410667586484</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.200502427336353</v>
+        <v>-7.262482347268289</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.232476353718317</v>
+        <v>0.2076843857455426</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.436208637836177</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.463948883115287</v>
+        <v>2.2513085662649</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.57548775350763</v>
+        <v>-7.637467673439566</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.08505373922123649</v>
+        <v>0.0602617712484621</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.811193964007455</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.241529203383951</v>
+        <v>2.028888886533563</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.935018076011632</v>
+        <v>-7.996997995943568</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.05340808648231388</v>
+        <v>-0.07820005445508826</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.811193964007455</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.246879506682001</v>
+        <v>2.034239189831613</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.261418104676645</v>
+        <v>-8.323398024608581</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1760520779911419</v>
+        <v>-0.2008440459639163</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.783193464588488</v>
+        <v>-2.137593992672468</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.058955509440171</v>
+        <v>1.846315192589783</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.254941957883085</v>
+        <v>-8.316921877815021</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1704198686519489</v>
+        <v>-0.1952118366247233</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.776717317794929</v>
+        <v>-2.131117845878908</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.065882948138076</v>
+        <v>1.853242631287688</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.251251032926675</v>
+        <v>-8.313230952858611</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168943498669385</v>
+        <v>-0.1937354666421593</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.776717317794929</v>
+        <v>-2.131117845878908</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.065882948138076</v>
+        <v>1.853242631287688</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.455509208256538</v>
+        <v>-8.517489128188474</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2451335716826879</v>
+        <v>-0.2699255396554623</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.904356262408918</v>
+        <v>-2.258756790492897</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.994812778488325</v>
+        <v>1.782172461637937</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.616148234744903</v>
+        <v>-8.678128154676839</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3049066277935979</v>
+        <v>-0.3296985957663723</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.019089735411313</v>
+        <v>-2.373490263495293</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.930455249171323</v>
+        <v>1.717814932320936</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.542678403077455</v>
+        <v>-8.60465832300939</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2601469936331973</v>
+        <v>-0.2849389616059717</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.945619903743865</v>
+        <v>-2.300020431827844</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.989908849665214</v>
+        <v>1.777268532814826</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.717802820463998</v>
+        <v>-8.779782740395934</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3156415398402976</v>
+        <v>-0.340433507813072</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.120744321130409</v>
+        <v>-2.475144849214388</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.899389419980804</v>
+        <v>1.686749103130416</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.952254914478488</v>
+        <v>-9.014234834410424</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4166415423476897</v>
+        <v>-0.4414335103204641</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.120744321130409</v>
+        <v>-2.475144849214388</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.892170255079208</v>
+        <v>1.67952993822882</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.240058759015726</v>
+        <v>-9.302038678947662</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5384352709365614</v>
+        <v>-0.5632272389093358</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.408548165667647</v>
+        <v>-2.762948693751626</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.712815757582889</v>
+        <v>1.500175440732501</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.469883206179551</v>
+        <v>-9.531863126111487</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6292492599635349</v>
+        <v>-0.6540412279363093</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.571195702737807</v>
+        <v>-2.925596230821787</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.616343025179349</v>
+        <v>1.403702708328961</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.701912125915813</v>
+        <v>-9.763892045847749</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7193670992289252</v>
+        <v>-0.7441590672016996</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.633208399926231</v>
+        <v>-2.98760892801021</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.581829135495409</v>
+        <v>1.369188818645022</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.649896611947</v>
+        <v>-9.999452069078139</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6945705579549988</v>
+        <v>-0.8343927408074543</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.633208399926231</v>
+        <v>-2.98760892801021</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.58581947118181</v>
+        <v>1.373179154331423</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.731188541501204</v>
+        <v>-10.08074399863234</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7285625566754224</v>
+        <v>-0.8683847395278779</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.633208399926231</v>
+        <v>-2.98760892801021</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.584344244283069</v>
+        <v>1.371703927432681</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.533919135773207</v>
+        <v>-9.883474592904346</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.634601384219351</v>
+        <v>-0.7744235670718065</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.435938994198232</v>
+        <v>-2.790339522282212</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.71775929788474</v>
+        <v>1.505118981034352</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.334767028536108</v>
+        <v>-9.684322485667247</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5679916749711946</v>
+        <v>-0.7078138578236501</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.270616468248419</v>
+        <v>-2.625016996332398</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.803901679807945</v>
+        <v>1.591261362957557</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.108921875816698</v>
+        <v>-9.458477332947837</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4680745408472218</v>
+        <v>-0.6078967236996773</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.228689792661255</v>
+        <v>-2.583090320745235</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.838636758196452</v>
+        <v>1.625996441346064</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.822647063494003</v>
+        <v>-9.172202520625142</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3524254713620851</v>
+        <v>-0.4922476542145406</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.228689792661255</v>
+        <v>-2.583090320745235</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.839775902752511</v>
+        <v>1.627135585902123</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.595851236420669</v>
+        <v>-8.945406693551808</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2590733663706439</v>
+        <v>-0.3988955492230994</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.160575848039711</v>
+        <v>-2.51497637612369</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.883278043687545</v>
+        <v>1.670637726837157</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.31194250549192</v>
+        <v>-8.661497962623059</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.1397761697605078</v>
+        <v>-0.2795983526129633</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.160575848039711</v>
+        <v>-2.51497637612369</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.889011747926181</v>
+        <v>1.676371431075794</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.064955255298969</v>
+        <v>-8.414510712430108</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.05071853207719235</v>
+        <v>-0.1905407149296479</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.913588597846759</v>
+        <v>-2.267989125930738</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.027466835648087</v>
+        <v>1.8148265187977</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.8011183880949</v>
+        <v>-8.150673845226038</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.04493273349152771</v>
+        <v>-0.0948894493609278</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.913588597846759</v>
+        <v>-2.267989125930738</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.01758335433518</v>
+        <v>1.804943037484792</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.533876587226503</v>
+        <v>-7.883432044357641</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.1499948933395125</v>
+        <v>0.01017271048705748</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.913588597846759</v>
+        <v>-2.267989125930738</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.015748793835806</v>
+        <v>1.803108476985418</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.258067423826019</v>
+        <v>-7.607622880957157</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.2600182437262455</v>
+        <v>0.12019606087379</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.824569289568025</v>
+        <v>-2.178969817652005</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.068860063829585</v>
+        <v>1.856219746979198</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.98899983605904</v>
+        <v>-7.338555293190177</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.3683137849785307</v>
+        <v>0.2284916021260757</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.555501701801046</v>
+        <v>-1.909902229885025</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.230969122635266</v>
+        <v>2.018328805784879</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.724939897736244</v>
+        <v>-7.074495354867381</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.460677444145897</v>
+        <v>0.3208552612934419</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.29144176347825</v>
+        <v>-1.645842291562229</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.376144769467192</v>
+        <v>2.163504452616805</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.017860274231405</v>
+        <v>-6.367415731362543</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.7407222598875314</v>
+        <v>0.6009000770350763</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.29144176347825</v>
+        <v>-1.645842291562229</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.373357735806891</v>
+        <v>2.160717418956504</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.768219244245453</v>
+        <v>-6.117774701376591</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.8409222957697535</v>
+        <v>0.7011001129172985</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.041800733492298</v>
+        <v>-1.396201261576278</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.523485977686303</v>
+        <v>2.310845660835916</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.513677344904378</v>
+        <v>-5.863232802035515</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.9421058767269406</v>
+        <v>0.8022836938744859</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7872588341512228</v>
+        <v>-1.141659362235202</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.675577938511706</v>
+        <v>2.462937621661318</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.28019612267478</v>
+        <v>-5.629751579805917</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.043422794456633</v>
+        <v>0.9036006116041775</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5537776119216242</v>
+        <v>-0.9081781400056035</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.823591100687318</v>
+        <v>2.61095078383693</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.100487592530907</v>
+        <v>-5.450043049662044</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.112413996201222</v>
+        <v>0.9725918133487674</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4966061077589281</v>
+        <v>-0.8510066358429074</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.855001792871976</v>
+        <v>2.642361476021589</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.968212118900021</v>
+        <v>-5.317767576031158</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.160691672400604</v>
+        <v>1.020869489548149</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3643306341280415</v>
+        <v>-0.7187311622120207</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.929734563797535</v>
+        <v>2.717094246947148</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.777612444226868</v>
+        <v>-5.127167901358005</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.239746602957502</v>
+        <v>1.099924420105047</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1737309594548886</v>
+        <v>-0.5281314875388678</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.046909429289063</v>
+        <v>2.834269112438676</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.528612645543287</v>
+        <v>-4.878168102674424</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.352252863654593</v>
+        <v>1.212430680802138</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1737309594548886</v>
+        <v>-0.5281314875388678</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.059815770512722</v>
+        <v>2.847175453662334</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.337233570682347</v>
+        <v>-4.686789027813484</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.30082856399975</v>
+        <v>1.161006381147295</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.01764811540605149</v>
+        <v>-0.3367524126779278</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.046667285830067</v>
+        <v>2.83402696897968</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.05820627502672</v>
+        <v>-4.407761732157857</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.460983824139087</v>
+        <v>1.321161641286633</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.01764811540605149</v>
+        <v>-0.3367524126779278</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.095211627707154</v>
+        <v>2.882571310856766</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.781468100355907</v>
+        <v>-4.131023557487044</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.575058105993407</v>
+        <v>1.435235923140952</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.1994647765159773</v>
+        <v>-0.154935751568002</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.207680636359104</v>
+        <v>2.995040319508716</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.654575693920838</v>
+        <v>-4.004131151051974</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.617101082313957</v>
+        <v>1.477278899461502</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.3263571829510472</v>
+        <v>-0.02804334513293205</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.275102093966668</v>
+        <v>3.06246177711628</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.466988186010911</v>
+        <v>-3.816543643142047</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.685175473382834</v>
+        <v>1.54535329053038</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.3263571829510472</v>
+        <v>-0.02804334513293205</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.268141481871575</v>
+        <v>3.055501165021187</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.224839792557053</v>
+        <v>-3.574395249688189</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.796497185145521</v>
+        <v>1.656675002293066</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.3263571829510472</v>
+        <v>-0.02804334513293205</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.282603836252718</v>
+        <v>3.06996351940233</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.161610420788704</v>
+        <v>-3.51116587791984</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.816321054312055</v>
+        <v>1.676498871459601</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.3263571829510472</v>
+        <v>-0.02804334513293205</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.277135956711913</v>
+        <v>3.064495639861525</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.975122728411698</v>
+        <v>-3.324678185542834</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.888414225273435</v>
+        <v>1.74859204242098</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.5128448753280535</v>
+        <v>0.1584443472440742</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.386526666148693</v>
+        <v>3.173886349298306</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-2.953973529508255</v>
+        <v>-3.303528986639391</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.904574883072138</v>
+        <v>1.764752700219683</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.5339940742314968</v>
+        <v>0.1795935461475175</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.406917163728085</v>
+        <v>3.194276846877697</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.829079198497429</v>
+        <v>3.82907919849743</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.71020808752481</v>
+        <v>-3.059763544655947</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.997861768212566</v>
+        <v>1.858039585360111</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.5339940742314968</v>
+        <v>0.1795935461475175</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.402697872075136</v>
+        <v>3.190057555224748</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.563423497364743</v>
+        <v>3.436329849136969</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.91570302597819</v>
+        <v>2.830980673592119</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.71020808752481</v>
+        <v>-3.059763544655947</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.997861768212566</v>
+        <v>1.858039585360111</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.5339940742314968</v>
+        <v>0.1795935461475175</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.908766822964557</v>
+        <v>2.824044470578487</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240329.xlsx
+++ b/tame_output/ON/bt/strategyON_20240329.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>125.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-575.3%</t>
+          <t>-577.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.7%</t>
+          <t>-66.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>509.0%</t>
+          <t>510.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-467.5%</t>
+          <t>-441.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-230.5%</t>
+          <t>-231.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.3%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-67.3%</t>
+          <t>-59.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-190.4%</t>
+          <t>-179.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-316.7%</t>
+          <t>-319.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.5%</t>
+          <t>-162.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-206.0%</t>
+          <t>-208.4%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-190.4%</t>
+          <t>-191.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.1572386040778024</v>
+        <v>-0.181080277093336</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.055901692501098</v>
+        <v>3.046365023294884</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.494192487848576</v>
+        <v>1.470350814833043</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.015669051155112</v>
+        <v>4.001364047345792</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.555387035031063</v>
+        <v>-0.5792287080465965</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.894569211624857</v>
+        <v>2.885032542418644</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.096044056895316</v>
+        <v>1.072202383879782</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.774706884088219</v>
+        <v>3.760401880278899</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7770089685891806</v>
+        <v>-0.8008506416047141</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.805786654800531</v>
+        <v>2.796249985594318</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.058517923207946</v>
+        <v>1.034676250192413</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.752057420474719</v>
+        <v>3.737752416665399</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9850130269422578</v>
+        <v>-1.008854699957791</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.727477176013226</v>
+        <v>2.717940506807012</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.058517923207946</v>
+        <v>1.034676250192413</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.756949565028644</v>
+        <v>3.742644561219325</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.255412989651143</v>
+        <v>-1.279254662666677</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.61439864726766</v>
+        <v>2.604861978061447</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7881179604990611</v>
+        <v>0.7642762874835276</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.589791043741302</v>
+        <v>3.575486039931981</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.594571367239665</v>
+        <v>-1.618413040255199</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.4718195955387</v>
+        <v>2.462282926332487</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4489595829105391</v>
+        <v>0.4251179098950055</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.379380316494637</v>
+        <v>3.365075312685317</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.922588588967144</v>
+        <v>-1.946430261982678</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.360950996586477</v>
+        <v>2.351414327380263</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1209423611830599</v>
+        <v>0.09710068816752637</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.202908273196918</v>
+        <v>3.188603269387598</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.919251842458173</v>
+        <v>-1.943093515473706</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.370384445598634</v>
+        <v>2.360847776392421</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1236343936020913</v>
+        <v>0.09979272058655775</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.212622243056905</v>
+        <v>3.198317239247585</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.285962894124719</v>
+        <v>-2.309804567140252</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.224806416975748</v>
+        <v>2.215269747769534</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2430766580644543</v>
+        <v>-0.2669183310799879</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.99370200410071</v>
+        <v>2.97939700029139</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.671143285054791</v>
+        <v>-2.694984958070324</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.069276799416582</v>
+        <v>2.059740130210369</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2430766580644543</v>
+        <v>-0.2669183310799879</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.992244542913574</v>
+        <v>2.977939539104253</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.014826058281454</v>
+        <v>-3.038667731296987</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.933572813580533</v>
+        <v>1.92403614437432</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3509827100916725</v>
+        <v>-0.3748243831072061</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.929270035151859</v>
+        <v>2.914965031342539</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.372476408519802</v>
+        <v>-3.396318081535335</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.786618732141452</v>
+        <v>1.777082062935238</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7086330603300206</v>
+        <v>-0.7324747333455541</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.710785883665108</v>
+        <v>2.696480879855788</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.37913734874195</v>
+        <v>-3.402979021757483</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.785727282752852</v>
+        <v>1.776190613546639</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7086330603300206</v>
+        <v>-0.7324747333455541</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.712558810365367</v>
+        <v>2.698253806556047</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.810943141891737</v>
+        <v>-3.834784814907271</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.599337852960342</v>
+        <v>1.589801183754128</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8450505567712876</v>
+        <v>-0.8688922297868211</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.617041199968011</v>
+        <v>2.602736196158691</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.137375670759481</v>
+        <v>-4.161217343775014</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.457049616415335</v>
+        <v>1.447512947209121</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9275188072784357</v>
+        <v>-0.9513604802939692</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.555845024665814</v>
+        <v>2.541540020856493</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.138939821869784</v>
+        <v>-4.162781494885317</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.455004547627179</v>
+        <v>1.445467878420965</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9275188072784357</v>
+        <v>-0.9513604802939692</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.554425616321779</v>
+        <v>2.540120612512458</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.502566066770098</v>
+        <v>-4.526407739785631</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.316041609901295</v>
+        <v>1.306504940695081</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.025740444145562</v>
+        <v>-1.049582117161095</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.501980194435744</v>
+        <v>2.487675190626424</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.500139002241379</v>
+        <v>-4.523980675256912</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.316266950718614</v>
+        <v>1.3067302815124</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.026073225952713</v>
+        <v>-1.049914898968247</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.501035040357285</v>
+        <v>2.486730036547965</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.908727779422058</v>
+        <v>-4.932569452437591</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.151592983861101</v>
+        <v>1.142056314654887</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.434662003133392</v>
+        <v>-1.458503676148925</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.254643318063637</v>
+        <v>2.240338314254317</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.321710263563152</v>
+        <v>-5.345551936578685</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.9815854226761243</v>
+        <v>0.9720487534699105</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.434662003133392</v>
+        <v>-1.458503676148925</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.249828750535098</v>
+        <v>2.235523746725777</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.73810213785015</v>
+        <v>-5.761943810865683</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8130227235702026</v>
+        <v>0.8034860543639888</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.434662003133392</v>
+        <v>-1.458503676148925</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.247822801143975</v>
+        <v>2.233517797334655</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.114779148379994</v>
+        <v>-6.138620821395527</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.6726106100269438</v>
+        <v>0.66307394082073</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.434662003133392</v>
+        <v>-1.458503676148925</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.258081491812654</v>
+        <v>2.243776488003334</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.128494012705105</v>
+        <v>-6.152335685720638</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6632242294425943</v>
+        <v>0.653687560236381</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.434662003133392</v>
+        <v>-1.458503676148925</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.254181056958349</v>
+        <v>2.239876053149029</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.441318811950085</v>
+        <v>-6.465160484965618</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5364992297996034</v>
+        <v>0.5269625605933901</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.434662003133392</v>
+        <v>-1.458503676148925</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.25258597701335</v>
+        <v>2.23828097320403</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.446131850415422</v>
+        <v>-6.469973523430955</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5383529903426769</v>
+        <v>0.5288163211364632</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.436208637836177</v>
+        <v>-1.460050310851711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.255436972120887</v>
+        <v>2.241131968311567</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.879480958525658</v>
+        <v>-6.903322631541191</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3609870425641795</v>
+        <v>0.3514503733579657</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.436208637836177</v>
+        <v>-1.460050310851711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.251410667586484</v>
+        <v>2.237105663777164</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.262482347268289</v>
+        <v>-7.286324020283822</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2076843857455426</v>
+        <v>0.1981477165393293</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.436208637836177</v>
+        <v>-1.460050310851711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.2513085662649</v>
+        <v>2.23700356245558</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.637467673439566</v>
+        <v>-7.661309346455099</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.0602617712484621</v>
+        <v>0.05072510204224834</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.811193964007455</v>
+        <v>-1.835035637022988</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.028888886533563</v>
+        <v>2.014583882724243</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.996997995943568</v>
+        <v>-8.020839668959102</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.07820005445508826</v>
+        <v>-0.08773672366130203</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.811193964007455</v>
+        <v>-1.835035637022988</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.034239189831613</v>
+        <v>2.019934186022294</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.323398024608581</v>
+        <v>-8.347239697624115</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2008440459639163</v>
+        <v>-0.2103807151701296</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.137593992672468</v>
+        <v>-2.161435665688001</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.846315192589783</v>
+        <v>1.832010188780463</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.316921877815021</v>
+        <v>-8.340763550830555</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1952118366247233</v>
+        <v>-0.2047485058309371</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.131117845878908</v>
+        <v>-2.154959518894441</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.853242631287688</v>
+        <v>1.838937627478368</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.313230952858611</v>
+        <v>-8.337072625874145</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1937354666421593</v>
+        <v>-0.2032721358483727</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.131117845878908</v>
+        <v>-2.154959518894441</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.853242631287688</v>
+        <v>1.838937627478368</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.517489128188474</v>
+        <v>-8.541330801204008</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2699255396554623</v>
+        <v>-0.2794622088616761</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.258756790492897</v>
+        <v>-2.28259846350843</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.782172461637937</v>
+        <v>1.767867457828617</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.678128154676839</v>
+        <v>-8.701969827692373</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3296985957663723</v>
+        <v>-0.339235264972586</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.373490263495293</v>
+        <v>-2.397331936510826</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.717814932320936</v>
+        <v>1.703509928511616</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.60465832300939</v>
+        <v>-8.628499996024924</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2849389616059717</v>
+        <v>-0.294475630812185</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.300020431827844</v>
+        <v>-2.323862104843378</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.777268532814826</v>
+        <v>1.762963529005506</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.779782740395934</v>
+        <v>-8.803624413411468</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.340433507813072</v>
+        <v>-0.3499701770192858</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.475144849214388</v>
+        <v>-2.498986522229921</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.686749103130416</v>
+        <v>1.672444099321096</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.014234834410424</v>
+        <v>-9.038076507425957</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4414335103204641</v>
+        <v>-0.4509701795266774</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.475144849214388</v>
+        <v>-2.498986522229921</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.67952993822882</v>
+        <v>1.6652249344195</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.302038678947662</v>
+        <v>-9.325880351963196</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5632272389093358</v>
+        <v>-0.5727639081155491</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.762948693751626</v>
+        <v>-2.78679036676716</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.500175440732501</v>
+        <v>1.485870436923181</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.531863126111487</v>
+        <v>-9.555704799127021</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6540412279363093</v>
+        <v>-0.663577897142523</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.925596230821787</v>
+        <v>-2.94943790383732</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.403702708328961</v>
+        <v>1.389397704519641</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.763892045847749</v>
+        <v>-9.787733718863283</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7441590672016996</v>
+        <v>-0.7536957364079129</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.98760892801021</v>
+        <v>-3.011450601025743</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.369188818645022</v>
+        <v>1.354883814835702</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.999452069078139</v>
+        <v>-9.73571820489447</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.8343927408074543</v>
+        <v>-0.7288991951339869</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.98760892801021</v>
+        <v>-3.011450601025743</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.373179154331423</v>
+        <v>1.358874150522103</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.08074399863234</v>
+        <v>-9.817010134448674</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8683847395278779</v>
+        <v>-0.7628911938544105</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.98760892801021</v>
+        <v>-3.011450601025743</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.371703927432681</v>
+        <v>1.357398923623361</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.883474592904346</v>
+        <v>-9.619740728720677</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7744235670718065</v>
+        <v>-0.6689300213983391</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.790339522282212</v>
+        <v>-2.814181195297745</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.505118981034352</v>
+        <v>1.490813977225032</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.684322485667247</v>
+        <v>-9.420588621483578</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.7078138578236501</v>
+        <v>-0.6023203121501823</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.625016996332398</v>
+        <v>-2.648858669347932</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.591261362957557</v>
+        <v>1.576956359148237</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.458477332947837</v>
+        <v>-9.194743468764166</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.6078967236996773</v>
+        <v>-0.502403178026209</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.583090320745235</v>
+        <v>-2.606931993760768</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.625996441346064</v>
+        <v>1.611691437536744</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.172202520625142</v>
+        <v>-8.908468656441471</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4922476542145406</v>
+        <v>-0.3867541085410724</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.583090320745235</v>
+        <v>-2.606931993760768</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.627135585902123</v>
+        <v>1.612830582092803</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.945406693551808</v>
+        <v>-8.681672829368138</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3988955492230994</v>
+        <v>-0.2934020035496312</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.51497637612369</v>
+        <v>-2.538818049139224</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.670637726837157</v>
+        <v>1.656332723027837</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.661497962623059</v>
+        <v>-8.397764098439389</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2795983526129633</v>
+        <v>-0.174104806939495</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.51497637612369</v>
+        <v>-2.538818049139224</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.676371431075794</v>
+        <v>1.662066427266474</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.414510712430108</v>
+        <v>-8.150776848246437</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.1905407149296479</v>
+        <v>-0.08504716925617961</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.267989125930738</v>
+        <v>-2.291830798946272</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.8148265187977</v>
+        <v>1.80052151498838</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.150673845226038</v>
+        <v>-7.886939981042368</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.0948894493609278</v>
+        <v>0.01060409631254045</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.267989125930738</v>
+        <v>-2.291830798946272</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.804943037484792</v>
+        <v>1.790638033675472</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.883432044357641</v>
+        <v>-7.619698180173971</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.01017271048705748</v>
+        <v>0.1156662561605253</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.267989125930738</v>
+        <v>-2.291830798946272</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.803108476985418</v>
+        <v>1.788803473176098</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.607622880957157</v>
+        <v>-7.343889016773487</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.12019606087379</v>
+        <v>0.2256896065472582</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.178969817652005</v>
+        <v>-2.202811490667538</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.856219746979198</v>
+        <v>1.841914743169878</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567245</v>
+        <v>3.800825778567243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.338555293190177</v>
+        <v>-7.074821429006508</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.2284916021260757</v>
+        <v>0.3339851477995435</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.909902229885025</v>
+        <v>-1.933743902900559</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.018328805784879</v>
+        <v>2.004023801975559</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.074495354867381</v>
+        <v>-6.810761490683712</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.3208552612934419</v>
+        <v>0.4263488069669097</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.645842291562229</v>
+        <v>-1.669683964577763</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.163504452616805</v>
+        <v>2.149199448807484</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.367415731362543</v>
+        <v>-6.103681867178874</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.6009000770350763</v>
+        <v>0.7063936227085441</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.645842291562229</v>
+        <v>-1.669683964577763</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.160717418956504</v>
+        <v>2.146412415147184</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.117774701376591</v>
+        <v>-5.854040837192922</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.7011001129172985</v>
+        <v>0.8065936585907663</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.396201261576278</v>
+        <v>-1.420042934591811</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.310845660835916</v>
+        <v>2.296540657026596</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.863232802035515</v>
+        <v>-5.599498937851846</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.8022836938744859</v>
+        <v>0.9077772395479533</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.141659362235202</v>
+        <v>-1.165501035250736</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.462937621661318</v>
+        <v>2.448632617851998</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.629751579805917</v>
+        <v>-5.366017715622248</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.9036006116041775</v>
+        <v>1.009094157277645</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9081781400056035</v>
+        <v>-0.932019813021137</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.61095078383693</v>
+        <v>2.59664578002761</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.450043049662044</v>
+        <v>-5.186309185478375</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.9725918133487674</v>
+        <v>1.078085359022235</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8510066358429074</v>
+        <v>-0.8748483088584409</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.642361476021589</v>
+        <v>2.628056472212268</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.317767576031158</v>
+        <v>-5.054033711847489</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.020869489548149</v>
+        <v>1.126363035221617</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7187311622120207</v>
+        <v>-0.7425728352275542</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.717094246947148</v>
+        <v>2.702789243137827</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.127167901358005</v>
+        <v>-4.863434037174336</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.099924420105047</v>
+        <v>1.205417965778514</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5281314875388678</v>
+        <v>-0.5519731605544014</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.834269112438676</v>
+        <v>2.819964108629356</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.878168102674424</v>
+        <v>-4.614434238490755</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.212430680802138</v>
+        <v>1.317924226475605</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5281314875388678</v>
+        <v>-0.5519731605544014</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.847175453662334</v>
+        <v>2.832870449853014</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.686789027813484</v>
+        <v>-4.423055163629815</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.161006381147295</v>
+        <v>1.266499926820763</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3367524126779278</v>
+        <v>-0.3605940856934613</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.83402696897968</v>
+        <v>2.81972196517036</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.407761732157857</v>
+        <v>-4.144027867974188</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.321161641286633</v>
+        <v>1.4266551869601</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3367524126779278</v>
+        <v>-0.3605940856934613</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.882571310856766</v>
+        <v>2.868266307047446</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.131023557487044</v>
+        <v>-3.867289693303376</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.435235923140952</v>
+        <v>1.54072946881442</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.154935751568002</v>
+        <v>-0.1787774245835355</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.995040319508716</v>
+        <v>2.980735315699396</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.004131151051974</v>
+        <v>-3.740397286868306</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.477278899461502</v>
+        <v>1.58277244513497</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.02804334513293205</v>
+        <v>-0.05188501814846558</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.06246177711628</v>
+        <v>3.04815677330696</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.816543643142047</v>
+        <v>-3.552809778958379</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.54535329053038</v>
+        <v>1.650846836203847</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.02804334513293205</v>
+        <v>-0.05188501814846558</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.055501165021187</v>
+        <v>3.041196161211867</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.574395249688189</v>
+        <v>-3.310661385504521</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.656675002293066</v>
+        <v>1.762168547966533</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.02804334513293205</v>
+        <v>-0.05188501814846558</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.06996351940233</v>
+        <v>3.05565851559301</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.51116587791984</v>
+        <v>-3.247432013736173</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.676498871459601</v>
+        <v>1.781992417133068</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.02804334513293205</v>
+        <v>-0.05188501814846558</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.064495639861525</v>
+        <v>3.050190636052205</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.324678185542834</v>
+        <v>-3.060944321359166</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.74859204242098</v>
+        <v>1.854085588094447</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.1584443472440742</v>
+        <v>0.1346026742285407</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.173886349298306</v>
+        <v>3.159581345488986</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.303528986639391</v>
+        <v>-3.039795122455723</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.764752700219683</v>
+        <v>1.87024624589315</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.1795935461475175</v>
+        <v>0.155751873131984</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.194276846877697</v>
+        <v>3.179971843068377</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.82907919849743</v>
+        <v>3.829079198497429</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.059763544655947</v>
+        <v>-2.796029680472278</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.858039585360111</v>
+        <v>1.963533131033579</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.1795935461475175</v>
+        <v>0.155751873131984</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.190057555224748</v>
+        <v>3.175752551415428</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,19 +45659,19 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.436329849136969</v>
+        <v>3.436329849136968</v>
       </c>
       <c r="C1918" t="n">
         <v>2.830980673592119</v>
       </c>
       <c r="D1918" t="n">
-        <v>-3.059763544655947</v>
+        <v>-2.796029680472278</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.858039585360111</v>
+        <v>1.963533131033579</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1795935461475175</v>
+        <v>0.155751873131984</v>
       </c>
       <c r="G1918" t="n">
         <v>2.824044470578487</v>

--- a/tame_output/ON/bt/strategyON_20240329.xlsx
+++ b/tame_output/ON/bt/strategyON_20240329.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-69.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.2%</t>
+          <t>125.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.1%</t>
+          <t>-63.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>510.2%</t>
+          <t>510.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-441.2%</t>
+          <t>-417.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-59.6%</t>
+          <t>-60.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-179.9%</t>
+          <t>-170.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>118.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-208.4%</t>
+          <t>-189.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-163.6%</t>
+          <t>-116.6%</t>
         </is>
       </c>
     </row>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -45662,19 +45662,19 @@
         <v>3.436329849136968</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.830980673592119</v>
+        <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.796029680472278</v>
+        <v>-2.556309799083474</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.963533131033579</v>
+        <v>2.061545397509116</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.155751873131984</v>
+        <v>0.3488933528618321</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.824044470578487</v>
+        <v>3.293761753173353</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240329.xlsx
+++ b/tame_output/ON/bt/strategyON_20240329.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>50.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.1%</t>
+          <t>-69.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-577.7%</t>
+          <t>-579.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-63.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>510.9%</t>
+          <t>513.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-417.2%</t>
+          <t>-417.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-231.5%</t>
+          <t>-232.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-60.2%</t>
+          <t>-58.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-170.1%</t>
+          <t>-170.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-319.1%</t>
+          <t>-320.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>118.3%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-162.2%</t>
+          <t>-212.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-189.1%</t>
+          <t>-188.4%</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-191.9%</t>
+          <t>-192.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-116.6%</t>
+          <t>-116.2%</t>
         </is>
       </c>
     </row>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.5792287080465965</v>
+        <v>-0.5933612059939077</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.885032542418644</v>
+        <v>2.879379543239719</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.072202383879782</v>
+        <v>1.058069885932471</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.760401880278899</v>
+        <v>3.751922381510512</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.8008506416047141</v>
+        <v>-0.8149831395520253</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.796249985594318</v>
+        <v>2.790596986415394</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.034676250192413</v>
+        <v>1.020543752245102</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.737752416665399</v>
+        <v>3.729272917897013</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.008854699957791</v>
+        <v>-1.022987197905102</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.717940506807012</v>
+        <v>2.712287507628088</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.034676250192413</v>
+        <v>1.020543752245102</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.742644561219325</v>
+        <v>3.734165062450938</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.279254662666677</v>
+        <v>-1.293387160613988</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.604861978061447</v>
+        <v>2.599208978882522</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7642762874835276</v>
+        <v>0.7501437895362164</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.575486039931981</v>
+        <v>3.567006541163595</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.618413040255199</v>
+        <v>-1.63254553820251</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.462282926332487</v>
+        <v>2.456629927153562</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4251179098950055</v>
+        <v>0.4109854119476943</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.365075312685317</v>
+        <v>3.35659581391693</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.946430261982678</v>
+        <v>-1.960562759929989</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.351414327380263</v>
+        <v>2.345761328201339</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.09710068816752637</v>
+        <v>0.08296819022021518</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.188603269387598</v>
+        <v>3.180123770619211</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.943093515473706</v>
+        <v>-1.957226013421017</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.360847776392421</v>
+        <v>2.355194777213496</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.09979272058655775</v>
+        <v>0.08566022263924655</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.198317239247585</v>
+        <v>3.189837740479199</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.309804567140252</v>
+        <v>-2.323937065087563</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.215269747769534</v>
+        <v>2.20961674859061</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2669183310799879</v>
+        <v>-0.2810508290272991</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.97939700029139</v>
+        <v>2.970917501523004</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.694984958070324</v>
+        <v>-2.709117456017635</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.059740130210369</v>
+        <v>2.054087131031444</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2669183310799879</v>
+        <v>-0.2810508290272991</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.977939539104253</v>
+        <v>2.969460040335867</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.038667731296987</v>
+        <v>-3.052800229244298</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.92403614437432</v>
+        <v>1.918383145195396</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3748243831072061</v>
+        <v>-0.3889568810545173</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.914965031342539</v>
+        <v>2.906485532574152</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.396318081535335</v>
+        <v>-3.410450579482646</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.777082062935238</v>
+        <v>1.771429063756314</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7324747333455541</v>
+        <v>-0.7466072312928653</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.696480879855788</v>
+        <v>2.688001381087401</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.402979021757483</v>
+        <v>-3.417111519704794</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.776190613546639</v>
+        <v>1.770537614367714</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7324747333455541</v>
+        <v>-0.7466072312928653</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.698253806556047</v>
+        <v>2.689774307787661</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.834784814907271</v>
+        <v>-3.848917312854582</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.589801183754128</v>
+        <v>1.584148184575204</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8688922297868211</v>
+        <v>-0.8830247277341323</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.602736196158691</v>
+        <v>2.594256697390305</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.161217343775014</v>
+        <v>-4.175349841722326</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.447512947209121</v>
+        <v>1.441859948030197</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9513604802939692</v>
+        <v>-0.9654929782412804</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.541540020856493</v>
+        <v>2.533060522088106</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.162781494885317</v>
+        <v>-4.176913992832629</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.445467878420965</v>
+        <v>1.439814879242041</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9513604802939692</v>
+        <v>-0.9654929782412804</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.540120612512458</v>
+        <v>2.531641113744072</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.526407739785631</v>
+        <v>-4.540540237732943</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.306504940695081</v>
+        <v>1.300851941516157</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.049582117161095</v>
+        <v>-1.063714615108406</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.487675190626424</v>
+        <v>2.479195691858038</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.523980675256912</v>
+        <v>-4.538113173204224</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.3067302815124</v>
+        <v>1.301077282333476</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.049914898968247</v>
+        <v>-1.064047396915558</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.486730036547965</v>
+        <v>2.478250537779578</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.932569452437591</v>
+        <v>-4.946701950384902</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.142056314654887</v>
+        <v>1.136403315475963</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.458503676148925</v>
+        <v>-1.472636174096236</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.240338314254317</v>
+        <v>2.23185881548593</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.345551936578685</v>
+        <v>-5.359684434525996</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.9720487534699105</v>
+        <v>0.9663957542909865</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.458503676148925</v>
+        <v>-1.472636174096236</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.235523746725777</v>
+        <v>2.227044247957391</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.761943810865683</v>
+        <v>-5.776076308812994</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8034860543639888</v>
+        <v>0.7978330551850648</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.458503676148925</v>
+        <v>-1.472636174096236</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.233517797334655</v>
+        <v>2.225038298566268</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.138620821395527</v>
+        <v>-6.152753319342838</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.66307394082073</v>
+        <v>0.657420941641806</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.458503676148925</v>
+        <v>-1.472636174096236</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.243776488003334</v>
+        <v>2.235296989234947</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.152335685720638</v>
+        <v>-6.166468183667949</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.653687560236381</v>
+        <v>0.6480345610574569</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.458503676148925</v>
+        <v>-1.472636174096236</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.239876053149029</v>
+        <v>2.231396554380642</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.465160484965618</v>
+        <v>-6.479292982912929</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5269625605933901</v>
+        <v>0.521309561414466</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.458503676148925</v>
+        <v>-1.472636174096236</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.23828097320403</v>
+        <v>2.229801474435643</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.469973523430955</v>
+        <v>-6.484106021378266</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5288163211364632</v>
+        <v>0.5231633219575391</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.460050310851711</v>
+        <v>-1.474182808799022</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.241131968311567</v>
+        <v>2.23265246954318</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.903322631541191</v>
+        <v>-6.917455129488502</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3514503733579657</v>
+        <v>0.3457973741790417</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.460050310851711</v>
+        <v>-1.474182808799022</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.237105663777164</v>
+        <v>2.228626165008777</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.286324020283822</v>
+        <v>-7.300456518231133</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.1981477165393293</v>
+        <v>0.1924947173604052</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.460050310851711</v>
+        <v>-1.474182808799022</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.23700356245558</v>
+        <v>2.228524063687193</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.661309346455099</v>
+        <v>-7.67544184440241</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.05072510204224834</v>
+        <v>0.0450721028633243</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.835035637022988</v>
+        <v>-1.8491681349703</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.014583882724243</v>
+        <v>2.006104383955856</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.020839668959102</v>
+        <v>-8.034972166906412</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.08773672366130203</v>
+        <v>-0.09338972284022606</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.835035637022988</v>
+        <v>-1.8491681349703</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.019934186022294</v>
+        <v>2.011454687253907</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.347239697624115</v>
+        <v>-8.361372195571425</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2103807151701296</v>
+        <v>-0.2160337143490536</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.161435665688001</v>
+        <v>-2.175568163635313</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.832010188780463</v>
+        <v>1.823530690012076</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.340763550830555</v>
+        <v>-8.354896048777865</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2047485058309371</v>
+        <v>-0.2104015050098611</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.154959518894441</v>
+        <v>-2.169092016841753</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.838937627478368</v>
+        <v>1.830458128709981</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.337072625874145</v>
+        <v>-8.351205123821455</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2032721358483727</v>
+        <v>-0.2089251350272967</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.154959518894441</v>
+        <v>-2.169092016841753</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.838937627478368</v>
+        <v>1.830458128709981</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.541330801204008</v>
+        <v>-8.555463299151318</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2794622088616761</v>
+        <v>-0.2851152080406001</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.28259846350843</v>
+        <v>-2.296730961455742</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.767867457828617</v>
+        <v>1.75938795906023</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.701969827692373</v>
+        <v>-8.716102325639683</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.339235264972586</v>
+        <v>-0.3448882641515101</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.397331936510826</v>
+        <v>-2.411464434458138</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.703509928511616</v>
+        <v>1.695030429743229</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.628499996024924</v>
+        <v>-8.642632493972235</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.294475630812185</v>
+        <v>-0.300128629991109</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.323862104843378</v>
+        <v>-2.337994602790689</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.762963529005506</v>
+        <v>1.754484030237119</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.803624413411468</v>
+        <v>-8.817756911358778</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3499701770192858</v>
+        <v>-0.3556231761982098</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.498986522229921</v>
+        <v>-2.513119020177233</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.672444099321096</v>
+        <v>1.663964600552709</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.038076507425957</v>
+        <v>-9.052209005373268</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4509701795266774</v>
+        <v>-0.4566231787056014</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.498986522229921</v>
+        <v>-2.513119020177233</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.6652249344195</v>
+        <v>1.656745435651113</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.325880351963196</v>
+        <v>-9.340012849910506</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5727639081155491</v>
+        <v>-0.5784169072944731</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.78679036676716</v>
+        <v>-2.800922864714471</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.485870436923181</v>
+        <v>1.477390938154794</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.555704799127021</v>
+        <v>-9.569837297074331</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.663577897142523</v>
+        <v>-0.6692308963214471</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.94943790383732</v>
+        <v>-2.963570401784632</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389397704519641</v>
+        <v>1.380918205751254</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.787733718863283</v>
+        <v>-9.801866216810593</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7536957364079129</v>
+        <v>-0.7593487355868369</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.011450601025743</v>
+        <v>-3.025583098973055</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.354883814835702</v>
+        <v>1.346404316067315</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.73571820489447</v>
+        <v>-9.74985070284178</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.7288991951339869</v>
+        <v>-0.734552194312911</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.011450601025743</v>
+        <v>-3.025583098973055</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.358874150522103</v>
+        <v>1.350394651753716</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.817010134448674</v>
+        <v>-9.831142632395984</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7628911938544105</v>
+        <v>-0.7685441930333345</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.011450601025743</v>
+        <v>-3.025583098973055</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.357398923623361</v>
+        <v>1.348919424854974</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.619740728720677</v>
+        <v>-9.633873226667987</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6689300213983391</v>
+        <v>-0.6745830205772632</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.814181195297745</v>
+        <v>-2.828313693245057</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.490813977225032</v>
+        <v>1.482334478456645</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.420588621483578</v>
+        <v>-9.434721119430888</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6023203121501823</v>
+        <v>-0.6079733113291064</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.648858669347932</v>
+        <v>-2.662991167295243</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.576956359148237</v>
+        <v>1.56847686037985</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.194743468764166</v>
+        <v>-9.208875966711478</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.502403178026209</v>
+        <v>-0.508056177205134</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.606931993760768</v>
+        <v>-2.62106449170808</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.611691437536744</v>
+        <v>1.603211938768357</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.908468656441471</v>
+        <v>-8.922601154388783</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3867541085410724</v>
+        <v>-0.3924071077199969</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.606931993760768</v>
+        <v>-2.62106449170808</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.612830582092803</v>
+        <v>1.604351083324416</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.681672829368138</v>
+        <v>-8.695805327315449</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2934020035496312</v>
+        <v>-0.2990550027285561</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.538818049139224</v>
+        <v>-2.552950547086535</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.656332723027837</v>
+        <v>1.64785322425945</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.397764098439389</v>
+        <v>-8.411896596386701</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.174104806939495</v>
+        <v>-0.17975780611842</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.538818049139224</v>
+        <v>-2.552950547086535</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.662066427266474</v>
+        <v>1.653586928498087</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.150776848246437</v>
+        <v>-8.164909346193749</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.08504716925617961</v>
+        <v>-0.09070016843510453</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.291830798946272</v>
+        <v>-2.305963296893583</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.80052151498838</v>
+        <v>1.792042016219993</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.886939981042368</v>
+        <v>-7.90107247898968</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.01060409631254045</v>
+        <v>0.004951097133615523</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.291830798946272</v>
+        <v>-2.305963296893583</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.790638033675472</v>
+        <v>1.782158534907085</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.619698180173971</v>
+        <v>-7.633830678121283</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.1156662561605253</v>
+        <v>0.1100132569816004</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.291830798946272</v>
+        <v>-2.305963296893583</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.788803473176098</v>
+        <v>1.780323974407712</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781948</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.343889016773487</v>
+        <v>-7.358021514720799</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.2256896065472582</v>
+        <v>0.2200366073683333</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.202811490667538</v>
+        <v>-2.21694398861485</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.841914743169878</v>
+        <v>1.833435244401491</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567243</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.074821429006508</v>
+        <v>-7.08895392695382</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.3339851477995435</v>
+        <v>0.328332148620619</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.933743902900559</v>
+        <v>-1.94787640084787</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.004023801975559</v>
+        <v>1.995544303207172</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.810761490683712</v>
+        <v>-6.824893988631024</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.4263488069669097</v>
+        <v>0.4206958077879852</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.669683964577763</v>
+        <v>-1.683816462525074</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.149199448807484</v>
+        <v>2.140719950039098</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.103681867178874</v>
+        <v>-6.117814365126185</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.7063936227085441</v>
+        <v>0.7007406235296196</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.669683964577763</v>
+        <v>-1.683816462525074</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.146412415147184</v>
+        <v>2.137932916378797</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.854040837192922</v>
+        <v>-5.868173335140233</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.8065936585907663</v>
+        <v>0.8009406594118418</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.420042934591811</v>
+        <v>-1.434175432539122</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.296540657026596</v>
+        <v>2.288061158258209</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.599498937851846</v>
+        <v>-5.613631435799158</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.9077772395479533</v>
+        <v>0.9021242403690288</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.165501035250736</v>
+        <v>-1.179633533198047</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.448632617851998</v>
+        <v>2.440153119083611</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.366017715622248</v>
+        <v>-5.38015021356956</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.009094157277645</v>
+        <v>1.00344115809872</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.932019813021137</v>
+        <v>-0.9461523109684484</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.59664578002761</v>
+        <v>2.588166281259223</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.186309185478375</v>
+        <v>-5.200441683425687</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.078085359022235</v>
+        <v>1.07243235984331</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8748483088584409</v>
+        <v>-0.8889808068057523</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.628056472212268</v>
+        <v>2.619576973443881</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.054033711847489</v>
+        <v>-5.068166209794801</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.126363035221617</v>
+        <v>1.120710036042692</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7425728352275542</v>
+        <v>-0.7567053331748657</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.702789243137827</v>
+        <v>2.69430974436944</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.863434037174336</v>
+        <v>-4.877566535121648</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.205417965778514</v>
+        <v>1.19976496659959</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5519731605544014</v>
+        <v>-0.5661056585017128</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.819964108629356</v>
+        <v>2.811484609860969</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.614434238490755</v>
+        <v>-4.628566736438067</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.317924226475605</v>
+        <v>1.312271227296681</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5519731605544014</v>
+        <v>-0.5661056585017128</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.832870449853014</v>
+        <v>2.824390951084628</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.423055163629815</v>
+        <v>-4.437187661577127</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.266499926820763</v>
+        <v>1.260846927641838</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3605940856934613</v>
+        <v>-0.3747265836407727</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.81972196517036</v>
+        <v>2.811242466401973</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.144027867974188</v>
+        <v>-4.1581603659215</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.4266551869601</v>
+        <v>1.421002187781175</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3605940856934613</v>
+        <v>-0.3747265836407727</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.868266307047446</v>
+        <v>2.859786808279059</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.867289693303376</v>
+        <v>-3.881422191250687</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.54072946881442</v>
+        <v>1.535076469635495</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1787774245835355</v>
+        <v>-0.1929099225308469</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.980735315699396</v>
+        <v>2.97225581693101</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.740397286868306</v>
+        <v>-3.754529784815618</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.58277244513497</v>
+        <v>1.577119445956045</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.05188501814846558</v>
+        <v>-0.066017516095777</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.04815677330696</v>
+        <v>3.039677274538573</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.552809778958379</v>
+        <v>-3.566942276905691</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.650846836203847</v>
+        <v>1.645193837024922</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.05188501814846558</v>
+        <v>-0.066017516095777</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.041196161211867</v>
+        <v>3.03271666244348</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.310661385504521</v>
+        <v>-3.324793883451833</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.762168547966533</v>
+        <v>1.756515548787609</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.05188501814846558</v>
+        <v>-0.066017516095777</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.05565851559301</v>
+        <v>3.047179016824623</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.247432013736173</v>
+        <v>-3.261564511683484</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.781992417133068</v>
+        <v>1.776339417954143</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.05188501814846558</v>
+        <v>-0.066017516095777</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.050190636052205</v>
+        <v>3.041711137283818</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.060944321359166</v>
+        <v>-3.075076819306478</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.854085588094447</v>
+        <v>1.848432588915522</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.1346026742285407</v>
+        <v>0.1204701762812292</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.159581345488986</v>
+        <v>3.151101846720599</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.039795122455723</v>
+        <v>-3.053927620403035</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.87024624589315</v>
+        <v>1.864593246714225</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.155751873131984</v>
+        <v>0.1416193751846726</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.179971843068377</v>
+        <v>3.17149234429999</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.829079198497429</v>
+        <v>3.829079198497431</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.796029680472278</v>
+        <v>-2.81016217841959</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.963533131033579</v>
+        <v>1.957880131854654</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.155751873131984</v>
+        <v>0.1416193751846726</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.175752551415428</v>
+        <v>3.167273052647041</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.436329849136968</v>
+        <v>3.788872776866543</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.556309799083474</v>
+        <v>-2.561639373017639</v>
       </c>
       <c r="E1918" t="n">
-        <v>2.061545397509116</v>
+        <v>2.05941356793545</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.3488933528618321</v>
+        <v>0.3563506390622267</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.293761753173353</v>
+        <v>3.298236124893589</v>
       </c>
     </row>
   </sheetData>
